--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="355">
   <si>
     <t xml:space="preserve">CATÁLOGO BANCO DE SUPLEMENTOS — No editar este archivo con otras herramientas</t>
   </si>
@@ -124,60 +124,63 @@
     <t xml:space="preserve">true</t>
   </si>
   <si>
+    <t xml:space="preserve">Creatina Monohidrato 300g magali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supplements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creatines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creatina-star-300g.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Más Vendido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creatina monohidrato micronizada Star Nutrition 300g. Clínicamente probada para aumentar la fuerza, la potencia y la masa muscular magra. El suplemento más estudiado en nutrición deportiva.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300g en polvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin sabor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuerza y Potencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disolvé 1 porción (5g) en 200–300 ml de agua o jugo. Tomá una vez al día, preferentemente post-entrenamiento o con una comida. Etapa de carga opcional: 4 porciones diarias durante los primeros 5–7 días para saturar reservas más rápido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aumentá la fuerza máxima, la potencia explosiva y la masa muscular magra. La creatina es el suplemento más estudiado de la nutrición deportiva, con evidencia sólida para musculación, CrossFit, sprint y actividades de alta intensidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creatina-star-300g-tabla.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whey-gentech-500g-chocolate, combo-proteina-creatina-gentech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20la%20Creatina%20Monohidrato%20300g%20Star%20Nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creatina-granger-300g</t>
+  </si>
+  <si>
     <t xml:space="preserve">Creatina Monohidrato 300g</t>
   </si>
   <si>
-    <t xml:space="preserve">Star Nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">supplements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creatines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creatina-star-300g.webp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Más Vendido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creatina monohidrato micronizada Star Nutrition 300g. Clínicamente probada para aumentar la fuerza, la potencia y la masa muscular magra. El suplemento más estudiado en nutrición deportiva.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300g en polvo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin sabor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuerza y Potencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disolvé 1 porción (5g) en 200–300 ml de agua o jugo. Tomá una vez al día, preferentemente post-entrenamiento o con una comida. Etapa de carga opcional: 4 porciones diarias durante los primeros 5–7 días para saturar reservas más rápido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aumentá la fuerza máxima, la potencia explosiva y la masa muscular magra. La creatina es el suplemento más estudiado de la nutrición deportiva, con evidencia sólida para musculación, CrossFit, sprint y actividades de alta intensidad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creatina-star-300g-tabla.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whey-gentech-500g-chocolate, combo-proteina-creatina-gentech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20la%20Creatina%20Monohidrato%20300g%20Star%20Nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creatina-granger-300g</t>
-  </si>
-  <si>
     <t xml:space="preserve">Granger</t>
   </si>
   <si>
@@ -445,7 +448,13 @@
     <t xml:space="preserve">Maní</t>
   </si>
   <si>
+    <t xml:space="preserve">10 barras</t>
+  </si>
+  <si>
     <t xml:space="preserve">barrita-integra-mani-tabla.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barrita-pont,</t>
   </si>
   <si>
     <t xml:space="preserve">https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20la%20Barrita%20Integra%20Man%C3%AD</t>
@@ -1188,7 +1197,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB28"/>
-  <sheetFormatPr defaultColWidth="8.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.84"/>
@@ -1197,11 +1206,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="38.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="17.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.83"/>
@@ -1211,11 +1220,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="10.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="28.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="90.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="90.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="38.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="55.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="90.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="50.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="90.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="50.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1345,7 +1354,7 @@
         <v>36</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>676767</v>
+        <v>666</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>37</v>
@@ -1413,10 +1422,10 @@
         <v>32</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="0" t="s">
         <v>35</v>
@@ -1428,16 +1437,16 @@
         <v>28000</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>38</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S6" s="0" t="s">
         <v>41</v>
@@ -1452,19 +1461,19 @@
         <v>44</v>
       </c>
       <c r="W6" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X6" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y6" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z6" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA6" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1472,7 +1481,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>32</v>
@@ -1481,10 +1490,10 @@
         <v>32</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>35</v>
@@ -1496,40 +1505,40 @@
         <v>25500</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T7" s="0" t="s">
         <v>42</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V7" s="0" t="s">
         <v>44</v>
       </c>
       <c r="W7" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X7" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y7" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z7" s="0" t="s">
         <v>48</v>
       </c>
       <c r="AA7" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1537,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>32</v>
@@ -1546,22 +1555,22 @@
         <v>32</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I8" s="0" t="n">
         <v>34000</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>32</v>
@@ -1570,40 +1579,40 @@
         <v>2</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>32</v>
       </c>
       <c r="R8" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="V8" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W8" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y8" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z8" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA8" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1611,7 +1620,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>32</v>
@@ -1620,55 +1629,55 @@
         <v>32</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I9" s="0" t="n">
         <v>45000</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T9" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U9" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V9" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W9" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X9" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z9" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AA9" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1676,7 +1685,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>32</v>
@@ -1685,22 +1694,22 @@
         <v>32</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I10" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>32</v>
@@ -1709,34 +1718,34 @@
         <v>4</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T10" s="0" t="s">
         <v>42</v>
       </c>
       <c r="U10" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V10" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="W10" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X10" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y10" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA10" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1744,7 +1753,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>32</v>
@@ -1753,52 +1762,52 @@
         <v>32</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I11" s="0" t="n">
         <v>12000</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T11" s="0" t="s">
         <v>42</v>
       </c>
       <c r="U11" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V11" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W11" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X11" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Y11" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA11" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1806,7 +1815,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>32</v>
@@ -1815,55 +1824,55 @@
         <v>32</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I12" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K12" s="0" t="s">
         <v>38</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T12" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U12" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="V12" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W12" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X12" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Y12" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA12" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1871,7 +1880,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>32</v>
@@ -1880,55 +1889,58 @@
         <v>32</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I13" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>38</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T13" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W13" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X13" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Y13" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
+      </c>
+      <c r="Z13" s="0" t="s">
+        <v>143</v>
       </c>
       <c r="AA13" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1936,7 +1948,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>32</v>
@@ -1945,52 +1957,52 @@
         <v>32</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I14" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="T14" s="0" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="U14" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V14" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W14" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="X14" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Y14" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AA14" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1998,61 +2010,61 @@
         <v>8</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>32</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I15" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="T15" s="0" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W15" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="X15" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Y15" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA15" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2060,7 +2072,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>32</v>
@@ -2069,55 +2081,55 @@
         <v>32</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I16" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K16" s="0" t="s">
         <v>38</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R16" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="S16" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="T16" s="0" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="U16" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V16" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W16" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="X16" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Y16" s="0" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AA16" s="0" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2125,7 +2137,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>32</v>
@@ -2134,52 +2146,52 @@
         <v>32</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I17" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R17" s="0" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="S17" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="T17" s="0" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="U17" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V17" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W17" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="X17" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Y17" s="0" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AA17" s="0" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2187,7 +2199,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>32</v>
@@ -2196,52 +2208,52 @@
         <v>32</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I18" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O18" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R18" s="0" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="S18" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="T18" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="U18" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W18" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="X18" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Y18" s="0" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AA18" s="0" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2249,7 +2261,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>32</v>
@@ -2258,52 +2270,52 @@
         <v>32</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I19" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="O19" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R19" s="0" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="S19" s="0" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="T19" s="0" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="U19" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V19" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W19" s="0" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="X19" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Y19" s="0" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AA19" s="0" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2311,7 +2323,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>32</v>
@@ -2320,22 +2332,22 @@
         <v>32</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I20" s="0" t="n">
         <v>26500</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="M20" s="0" t="s">
         <v>32</v>
@@ -2344,40 +2356,40 @@
         <v>3</v>
       </c>
       <c r="O20" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P20" s="0" t="s">
         <v>32</v>
       </c>
       <c r="R20" s="0" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="S20" s="0" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="T20" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U20" s="0" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="V20" s="0" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="W20" s="0" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="X20" s="0" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Y20" s="0" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Z20" s="0" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AA20" s="0" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2385,7 +2397,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>32</v>
@@ -2394,49 +2406,49 @@
         <v>32</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I21" s="0" t="n">
         <v>42000</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O21" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R21" s="0" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="S21" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T21" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U21" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="V21" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="W21" s="0" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="X21" s="0" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AA21" s="0" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2444,7 +2456,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>32</v>
@@ -2453,49 +2465,49 @@
         <v>32</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I22" s="0" t="n">
         <v>42000</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O22" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R22" s="0" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S22" s="0" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="T22" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U22" s="0" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="V22" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="W22" s="0" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="X22" s="0" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AA22" s="0" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,7 +2515,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>32</v>
@@ -2512,49 +2524,49 @@
         <v>32</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I23" s="0" t="n">
         <v>56000</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="O23" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R23" s="0" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="S23" s="0" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="T23" s="0" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="U23" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="V23" s="0" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="W23" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="X23" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AA23" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2562,7 +2574,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>32</v>
@@ -2571,49 +2583,49 @@
         <v>32</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I24" s="0" t="n">
         <v>90000</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="O24" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R24" s="0" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="S24" s="0" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="T24" s="0" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="U24" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="W24" s="0" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="X24" s="0" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AA24" s="0" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2621,7 +2633,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>32</v>
@@ -2630,22 +2642,22 @@
         <v>32</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="O25" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="P25" s="0" t="s">
         <v>32</v>
@@ -2654,31 +2666,31 @@
         <v>32</v>
       </c>
       <c r="R25" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="S25" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="T25" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U25" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="W25" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="X25" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Z25" s="0" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AA25" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2686,7 +2698,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>32</v>
@@ -2695,49 +2707,49 @@
         <v>32</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I26" s="0" t="n">
         <v>40000</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="O26" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R26" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S26" s="0" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="T26" s="0" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="U26" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V26" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W26" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="X26" s="0" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AA26" s="0" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2745,7 +2757,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>32</v>
@@ -2754,49 +2766,49 @@
         <v>32</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="I27" s="0" t="n">
         <v>50000</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O27" s="0" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="R27" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="S27" s="0" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="T27" s="0" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="U27" s="0" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="V27" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W27" s="0" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="X27" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AA27" s="0" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2804,31 +2816,31 @@
         <v>14</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>32</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I28" s="0" t="n">
         <v>7400</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K28" s="0" t="s">
         <v>38</v>
@@ -2840,37 +2852,37 @@
         <v>5</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R28" s="0" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="S28" s="0" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="T28" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="U28" s="0" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="V28" s="0" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="W28" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="X28" s="0" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Y28" s="0" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Z28" s="0" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AA28" s="0" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2890,98 +2902,98 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.4921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2989,21 +3001,21 @@
         <v>30</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3023,179 +3035,179 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultColWidth="8.4921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3227,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.4921875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.83"/>
@@ -3223,12 +3235,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="2.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="2.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3242,7 +3254,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3261,66 +3273,66 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="0" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="0" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="0" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="0" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="358">
   <si>
     <t xml:space="preserve">CATÁLOGO BANCO DE SUPLEMENTOS — No editar este archivo con otras herramientas</t>
   </si>
@@ -884,6 +884,15 @@
   </si>
   <si>
     <t xml:space="preserve">https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20el%20Shaker%20ENA%20Plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrato-de-magnesio-granger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrato de Magnesio 144g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">citrato-de-magnesio-granger.webp</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIGURACIÓN DEL SITIO — Editá los valores en la columna 'valor'</t>
@@ -1097,7 +1106,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1119,6 +1128,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1170,12 +1185,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1196,7 +1215,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.83"/>
@@ -2885,6 +2904,38 @@
         <v>286</v>
       </c>
     </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
@@ -2911,89 +2962,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3001,21 +3052,21 @@
         <v>30</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3042,172 +3093,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -3240,7 +3291,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3254,7 +3305,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3279,7 +3330,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>158</v>
@@ -3293,7 +3344,7 @@
         <v>102</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3304,7 +3355,7 @@
         <v>124</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3312,7 +3363,7 @@
         <v>125</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="355">
   <si>
     <t xml:space="preserve">CATÁLOGO BANCO DE SUPLEMENTOS — No editar este archivo con otras herramientas</t>
   </si>
@@ -884,15 +884,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20el%20Shaker%20ENA%20Plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citrato-de-magnesio-granger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citrato de Magnesio 144g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">citrato-de-magnesio-granger.webp</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIGURACIÓN DEL SITIO — Editá los valores en la columna 'valor'</t>
@@ -2905,36 +2896,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>288</v>
-      </c>
-      <c r="F29" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H29" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="I29" s="0" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>289</v>
-      </c>
+      <c r="B29" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2962,89 +2924,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3052,21 +3014,21 @@
         <v>30</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3093,172 +3055,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -3291,7 +3253,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,7 +3267,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3330,7 +3292,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>158</v>
@@ -3344,7 +3306,7 @@
         <v>102</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3355,7 +3317,7 @@
         <v>124</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3363,7 +3325,7 @@
         <v>125</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="358">
   <si>
     <t xml:space="preserve">CATÁLOGO BANCO DE SUPLEMENTOS — No editar este archivo con otras herramientas</t>
   </si>
@@ -884,6 +884,15 @@
   </si>
   <si>
     <t xml:space="preserve">https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20el%20Shaker%20ENA%20Plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrato-de-magnesio-granger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrato de Magnesio 144g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">citrato-de-magnesio-granger.webp</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIGURACIÓN DEL SITIO — Editá los valores en la columna 'valor'</t>
@@ -2896,7 +2905,36 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="2"/>
+      <c r="A29" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>289</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2924,89 +2962,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3014,21 +3052,21 @@
         <v>30</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3055,172 +3093,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -3253,7 +3291,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3267,7 +3305,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3292,7 +3330,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>158</v>
@@ -3306,7 +3344,7 @@
         <v>102</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3317,7 +3355,7 @@
         <v>124</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3325,7 +3363,7 @@
         <v>125</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="364">
   <si>
     <t xml:space="preserve">CATÁLOGO BANCO DE SUPLEMENTOS — No editar este archivo con otras herramientas</t>
   </si>
@@ -893,6 +893,24 @@
   </si>
   <si>
     <t xml:space="preserve">citrato-de-magnesio-granger.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agotado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrato de Magnesio Granger 144g. Perfecto para el tussi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144g en polvo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descanso y Recuperación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no sé bien todavía como se usa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">para dormir como un dios papá.</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIGURACIÓN DEL SITIO — Editá los valores en la columna 'valor'</t>
@@ -1106,7 +1124,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1128,12 +1146,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1194,7 +1206,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1216,7 +1228,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB29"/>
-  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.84"/>
@@ -2935,6 +2947,30 @@
       <c r="J29" s="1" t="s">
         <v>289</v>
       </c>
+      <c r="O29" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="R29" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="S29" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="T29" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="U29" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="V29" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="W29" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="X29" s="0" t="s">
+        <v>295</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2953,7 +2989,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90.85"/>
@@ -2962,89 +2998,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3052,21 +3088,21 @@
         <v>30</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -3086,179 +3122,179 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -3278,7 +3314,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.83"/>
@@ -3291,7 +3327,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,7 +3341,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3330,7 +3366,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>158</v>
@@ -3344,7 +3380,7 @@
         <v>102</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3355,7 +3391,7 @@
         <v>124</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3363,7 +3399,7 @@
         <v>125</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="365">
   <si>
     <t xml:space="preserve">CATÁLOGO BANCO DE SUPLEMENTOS — No editar este archivo con otras herramientas</t>
   </si>
@@ -911,6 +911,9 @@
   </si>
   <si>
     <t xml:space="preserve">para dormir como un dios papá.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citrato-magnesio-tabla.webp</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIGURACIÓN DEL SITIO — Editá los valores en la columna 'valor'</t>
@@ -1130,7 +1133,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1227,8 +1229,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB29"/>
-  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB30"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.84"/>
@@ -1256,6 +1258,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="55.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="90.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="50.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="29" style="0" width="8.47"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2850,7 +2853,7 @@
         <v>274</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>32</v>
@@ -2950,6 +2953,9 @@
       <c r="O29" s="0" t="s">
         <v>290</v>
       </c>
+      <c r="P29" s="0" t="s">
+        <v>32</v>
+      </c>
       <c r="R29" s="0" t="s">
         <v>291</v>
       </c>
@@ -2970,6 +2976,14 @@
       </c>
       <c r="X29" s="0" t="s">
         <v>295</v>
+      </c>
+      <c r="Y29" s="0" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2989,120 +3003,121 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="4" style="0" width="8.47"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3122,179 +3137,180 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="2" style="0" width="8.47"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3314,7 +3330,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.46875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.83"/>
@@ -3323,14 +3339,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="2.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="8" style="0" width="8.47"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>9</v>
       </c>
@@ -3341,10 +3358,10 @@
         <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>35</v>
       </c>
@@ -3358,7 +3375,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>124</v>
       </c>
@@ -3366,13 +3383,13 @@
         <v>74</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G5" s="0" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>208</v>
       </c>
@@ -3380,10 +3397,10 @@
         <v>102</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>276</v>
       </c>
@@ -3391,33 +3408,33 @@
         <v>124</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="0" t="s">
         <v>125</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="0" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="0" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="0" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="0" t="s">
         <v>276</v>
       </c>

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -1229,7 +1229,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB30"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.83"/>
@@ -2981,11 +2981,6 @@
         <v>296</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="366">
   <si>
     <t xml:space="preserve">CATÁLOGO BANCO DE SUPLEMENTOS — No editar este archivo con otras herramientas</t>
   </si>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">true</t>
   </si>
   <si>
-    <t xml:space="preserve">Creatina Monohidrato 300g magali</t>
+    <t xml:space="preserve">Creatina Monohidrato 300g </t>
   </si>
   <si>
     <t xml:space="preserve">Star Nutrition</t>
@@ -211,6 +211,9 @@
     <t xml:space="preserve">creatina-gentech-250g</t>
   </si>
   <si>
+    <t xml:space="preserve">false</t>
+  </si>
+  <si>
     <t xml:space="preserve">Creatina Monohidrato 250g</t>
   </si>
   <si>
@@ -220,6 +223,9 @@
     <t xml:space="preserve">creatina-gentech-250g.webp</t>
   </si>
   <si>
+    <t xml:space="preserve">Agotado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Creatina monohidrato Gentech 250g. Alta pureza para maximizar el rendimiento, la fuerza y la recuperación muscular entre sesiones.</t>
   </si>
   <si>
@@ -499,9 +505,6 @@
     <t xml:space="preserve">barrita-crudda-coco</t>
   </si>
   <si>
-    <t xml:space="preserve">false</t>
-  </si>
-  <si>
     <t xml:space="preserve">Crudda Caja Coco y Chocolate (9G)</t>
   </si>
   <si>
@@ -709,6 +712,9 @@
     <t xml:space="preserve">Combo Mixto 3X Cajas Crudda / Integra</t>
   </si>
   <si>
+    <t xml:space="preserve">El Banco</t>
+  </si>
+  <si>
     <t xml:space="preserve">combo-mixto-3cajas-crudda-integra.png</t>
   </si>
   <si>
@@ -739,9 +745,6 @@
     <t xml:space="preserve">Combo Mixto 5X Cajas Crudda / Integra</t>
   </si>
   <si>
-    <t xml:space="preserve">El Banco</t>
-  </si>
-  <si>
     <t xml:space="preserve">combo-mixto-5cajas-crudda-integra.png</t>
   </si>
   <si>
@@ -895,10 +898,7 @@
     <t xml:space="preserve">citrato-de-magnesio-granger.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">Agotado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citrato de Magnesio Granger 144g. Perfecto para el tussi</t>
+    <t xml:space="preserve">Citrato de Magnesio Granger, ideal para complementar la ingesta diaria de magnesio y apoyar la función muscular, nerviosa y energética.</t>
   </si>
   <si>
     <t xml:space="preserve">144g en polvo</t>
@@ -907,13 +907,16 @@
     <t xml:space="preserve">Descanso y Recuperación</t>
   </si>
   <si>
-    <t xml:space="preserve">no sé bien todavía como se usa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">para dormir como un dios papá.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citrato-magnesio-tabla.webp</t>
+    <t xml:space="preserve">Tomá la porción indicada en el envase, preferentemente junto con una comida y agua. No superes la dosis recomendada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potenciá tu bienestar diario y acompañá cada entrenamiento con un mineral esencial para la función muscular, el sistema nervioso y la producción de energía.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">citrato-magnesio-tabla.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20el%Citrato%de%Magnesio</t>
   </si>
   <si>
     <t xml:space="preserve">CONFIGURACIÓN DEL SITIO — Editá los valores en la columna 'valor'</t>
@@ -1127,12 +1130,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1148,6 +1152,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1199,7 +1209,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1209,6 +1219,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1229,8 +1247,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB29"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB30"/>
+  <sheetFormatPr defaultColWidth="10.484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.84"/>
@@ -1388,7 +1406,7 @@
         <v>36</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>666</v>
+        <v>30000</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>37</v>
@@ -1521,13 +1539,13 @@
         <v>32</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>35</v>
@@ -1539,40 +1557,40 @@
         <v>25500</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T7" s="0" t="s">
         <v>42</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V7" s="0" t="s">
         <v>44</v>
       </c>
       <c r="W7" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="X7" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y7" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Z7" s="0" t="s">
         <v>48</v>
       </c>
       <c r="AA7" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1580,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>32</v>
@@ -1589,22 +1607,22 @@
         <v>32</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" s="0" t="n">
         <v>34000</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M8" s="0" t="s">
         <v>32</v>
@@ -1619,34 +1637,34 @@
         <v>32</v>
       </c>
       <c r="R8" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="V8" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W8" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Y8" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Z8" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AA8" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1654,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>32</v>
@@ -1663,55 +1681,55 @@
         <v>32</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" s="0" t="n">
         <v>45000</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O9" s="0" t="s">
         <v>54</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="S9" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="T9" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U9" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V9" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W9" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="X9" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y9" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Z9" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA9" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1719,7 +1737,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>32</v>
@@ -1728,22 +1746,22 @@
         <v>32</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G10" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I10" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M10" s="0" t="s">
         <v>32</v>
@@ -1755,31 +1773,31 @@
         <v>54</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T10" s="0" t="s">
         <v>42</v>
       </c>
       <c r="U10" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V10" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W10" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="X10" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Y10" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AA10" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1787,7 +1805,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>32</v>
@@ -1796,52 +1814,52 @@
         <v>32</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I11" s="0" t="n">
         <v>12000</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O11" s="0" t="s">
         <v>54</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T11" s="0" t="s">
         <v>42</v>
       </c>
       <c r="U11" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V11" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="W11" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="X11" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Y11" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AA11" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1849,7 +1867,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>32</v>
@@ -1858,22 +1876,22 @@
         <v>32</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I12" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K12" s="0" t="s">
         <v>38</v>
@@ -1882,31 +1900,31 @@
         <v>54</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T12" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="U12" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="V12" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W12" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X12" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Y12" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA12" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1914,7 +1932,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>32</v>
@@ -1923,22 +1941,22 @@
         <v>32</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I13" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K13" s="0" t="s">
         <v>38</v>
@@ -1947,34 +1965,34 @@
         <v>54</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T13" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W13" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X13" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Y13" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Z13" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AA13" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1982,7 +2000,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>32</v>
@@ -1991,52 +2009,52 @@
         <v>32</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I14" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O14" s="0" t="s">
         <v>54</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="T14" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="U14" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V14" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W14" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="X14" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y14" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AA14" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2044,61 +2062,61 @@
         <v>8</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>32</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I15" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="T15" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W15" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="X15" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y15" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA15" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2106,7 +2124,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>32</v>
@@ -2115,22 +2133,22 @@
         <v>32</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I16" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K16" s="0" t="s">
         <v>38</v>
@@ -2139,31 +2157,31 @@
         <v>54</v>
       </c>
       <c r="R16" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="S16" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="T16" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="U16" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V16" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W16" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="X16" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y16" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AA16" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2171,7 +2189,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>32</v>
@@ -2180,52 +2198,52 @@
         <v>32</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I17" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O17" s="0" t="s">
         <v>54</v>
       </c>
       <c r="R17" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="S17" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="T17" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U17" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V17" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W17" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="X17" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y17" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA17" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2233,7 +2251,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>32</v>
@@ -2242,52 +2260,52 @@
         <v>32</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I18" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O18" s="0" t="s">
         <v>54</v>
       </c>
       <c r="R18" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="S18" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="T18" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="U18" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W18" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="X18" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y18" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA18" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2295,7 +2313,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>32</v>
@@ -2304,52 +2322,52 @@
         <v>32</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I19" s="0" t="n">
         <v>20000</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O19" s="0" t="s">
         <v>54</v>
       </c>
       <c r="R19" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="S19" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="T19" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="U19" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V19" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W19" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="X19" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y19" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AA19" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2357,7 +2375,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>32</v>
@@ -2366,22 +2384,22 @@
         <v>32</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I20" s="0" t="n">
         <v>26500</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M20" s="0" t="s">
         <v>32</v>
@@ -2396,34 +2414,34 @@
         <v>32</v>
       </c>
       <c r="R20" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="S20" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T20" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U20" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V20" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="W20" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="X20" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y20" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z20" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA20" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2431,7 +2449,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>32</v>
@@ -2440,49 +2458,49 @@
         <v>32</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I21" s="0" t="n">
         <v>42000</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O21" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R21" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S21" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T21" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U21" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V21" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="W21" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="X21" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AA21" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2490,7 +2508,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>32</v>
@@ -2499,49 +2517,49 @@
         <v>32</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I22" s="0" t="n">
         <v>42000</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O22" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R22" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S22" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="T22" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U22" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V22" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="W22" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="X22" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA22" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2549,7 +2567,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>32</v>
@@ -2558,49 +2576,49 @@
         <v>32</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I23" s="0" t="n">
         <v>56000</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O23" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R23" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="S23" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="T23" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="U23" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V23" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="W23" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="X23" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AA23" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2608,7 +2626,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>32</v>
@@ -2617,49 +2635,58 @@
         <v>32</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I24" s="0" t="n">
         <v>90000</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="O24" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
+      </c>
+      <c r="P24" s="0" t="s">
+        <v>32</v>
       </c>
       <c r="R24" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S24" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="T24" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="U24" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="W24" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="X24" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA24" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2667,7 +2694,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>32</v>
@@ -2676,22 +2703,22 @@
         <v>32</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O25" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P25" s="0" t="s">
         <v>32</v>
@@ -2700,31 +2727,31 @@
         <v>32</v>
       </c>
       <c r="R25" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S25" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T25" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U25" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="W25" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="X25" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z25" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA25" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2732,7 +2759,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>32</v>
@@ -2741,49 +2768,49 @@
         <v>32</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I26" s="0" t="n">
         <v>40000</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O26" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R26" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S26" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T26" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U26" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="V26" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W26" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="X26" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA26" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2791,7 +2818,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>32</v>
@@ -2800,49 +2827,49 @@
         <v>32</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I27" s="0" t="n">
         <v>50000</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O27" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R27" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S27" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T27" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="U27" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V27" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W27" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X27" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA27" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2850,7 +2877,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>32</v>
@@ -2859,81 +2886,75 @@
         <v>32</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I28" s="0" t="n">
         <v>7400</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K28" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" s="0" t="n">
-        <v>5</v>
-      </c>
       <c r="O28" s="0" t="s">
         <v>54</v>
       </c>
       <c r="R28" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="S28" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T28" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="U28" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="V28" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="W28" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X28" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y28" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z28" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA28" s="0" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="25.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F29" s="0" t="s">
         <v>52</v>
@@ -2942,21 +2963,18 @@
         <v>35</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>290</v>
-      </c>
-      <c r="P29" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="R29" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>291</v>
       </c>
       <c r="S29" s="0" t="s">
@@ -2965,23 +2983,32 @@
       <c r="T29" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="U29" s="0" t="s">
-        <v>280</v>
+      <c r="U29" s="0" t="n">
+        <v>90</v>
       </c>
       <c r="V29" s="0" t="s">
         <v>293</v>
       </c>
-      <c r="W29" s="0" t="s">
+      <c r="W29" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="X29" s="0" t="s">
+      <c r="X29" s="3" t="s">
         <v>295</v>
       </c>
       <c r="Y29" s="0" t="s">
         <v>296</v>
       </c>
+      <c r="AA29" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R30" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="AA29" r:id="rId1" display="https://wa.me/5491124602875?text=Hola%2C%20me%20interesa%20el%Citrato%de%Magnesio"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2998,7 +3025,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90.85"/>
@@ -3008,89 +3035,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3098,21 +3125,21 @@
         <v>30</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -3132,7 +3159,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="2" style="0" width="8.47"/>
@@ -3140,172 +3167,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3325,7 +3352,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.83"/>
@@ -3339,7 +3366,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3353,7 +3380,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3372,66 +3399,66 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/catalogo_productos_banco.xlsx
+++ b/catalogo_productos_banco.xlsx
@@ -613,7 +613,7 @@
     <t xml:space="preserve">pont</t>
   </si>
   <si>
-    <t xml:space="preserve">Barrita-pont.png</t>
+    <t xml:space="preserve">barrita-pont.png</t>
   </si>
   <si>
     <t xml:space="preserve">Barrita formulada con un elevado aporte proteico, 18 g por unidad en su presentación comercial. La proteína permite complementar la ingesta diaria de aminoácidos, mientras que la fibra y el resto de los macronutrientes determinan su textura, densidad energética y respuesta digestiva. Su cobertura de chocolate combina funcionalidad nutricional con una experiencia similar a una golosina premium.</t>
@@ -1193,16 +1193,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1232,1789 +1224,1787 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB29"/>
-  <sheetFormatPr defaultColWidth="8.484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="74.39"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="19" style="1" width="8.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="220.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="188"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="37" min="25" style="1" width="8.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="74.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="220.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="188"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="P4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="W4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Y4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="Z4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AA4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AB4" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2" t="s">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="R5" s="3" t="s">
+      <c r="P5" s="1"/>
+      <c r="R5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="T5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="U5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="V5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="W5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y5" s="3" t="s">
+      <c r="Y5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="3" t="s">
+      <c r="Z5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AA5" s="3" t="s">
+      <c r="AA5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>28000</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N6" s="2" t="n">
+      <c r="M6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="4" t="s">
+      <c r="P6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="S6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="3" t="s">
+      <c r="T6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="U6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="V6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="W6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="X6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y6" s="3" t="s">
+      <c r="Y6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="Z6" s="3" t="s">
+      <c r="Z6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AA6" s="3" t="s">
+      <c r="AA6" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>26000</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="R7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="S7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="T7" s="3" t="s">
+      <c r="T7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="U7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="V7" s="3" t="s">
+      <c r="V7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W7" s="3" t="s">
+      <c r="W7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y7" s="3" t="s">
+      <c r="Y7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Z7" s="3" t="s">
+      <c r="Z7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AA7" s="3" t="s">
+      <c r="AA7" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="1" t="n">
         <v>34000</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="2" t="n">
+      <c r="M8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P8" s="2"/>
-      <c r="R8" s="4" t="s">
+      <c r="P8" s="1"/>
+      <c r="R8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="S8" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="T8" s="3" t="s">
+      <c r="T8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="U8" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="V8" s="3" t="s">
+      <c r="V8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="W8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="X8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Y8" s="3" t="s">
+      <c r="Y8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="Z8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AA8" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="1" t="n">
         <v>45000</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="R9" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="S9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="T9" s="3" t="s">
+      <c r="T9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="U9" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="V9" s="3" t="s">
+      <c r="V9" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="W9" s="3" t="s">
+      <c r="W9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="X9" s="3" t="s">
+      <c r="X9" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Y9" s="3" t="s">
+      <c r="Y9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Z9" s="3" t="s">
+      <c r="Z9" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AA9" s="3" t="s">
+      <c r="AA9" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2" t="s">
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="R10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="S10" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="T10" s="3" t="s">
+      <c r="T10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U10" s="3" t="s">
+      <c r="U10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V10" s="3" t="s">
+      <c r="V10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="X10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="Y10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Z10" s="3" t="s">
+      <c r="Z10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AA10" s="3" t="s">
+      <c r="AA10" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="1" t="n">
         <v>12000</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="R11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="T11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U11" s="3" t="s">
+      <c r="U11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V11" s="3" t="s">
+      <c r="V11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="W11" s="4" t="s">
+      <c r="W11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="X11" s="3" t="s">
+      <c r="X11" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Y11" s="3" t="s">
+      <c r="Y11" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="Z11" s="3" t="s">
+      <c r="Z11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AA11" s="3" t="s">
+      <c r="AA11" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="O12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="R12" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="S12" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T12" s="3" t="s">
+      <c r="T12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V12" s="3" t="s">
+      <c r="V12" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W12" s="3" t="s">
+      <c r="W12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="X12" s="4" t="s">
+      <c r="X12" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y12" s="3" t="s">
+      <c r="Y12" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="Z12" s="3" t="s">
+      <c r="Z12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AA12" s="3" t="s">
+      <c r="AA12" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" s="4" t="s">
+      <c r="P13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="S13" s="3" t="s">
+      <c r="S13" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T13" s="3" t="s">
+      <c r="T13" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V13" s="3" t="s">
+      <c r="V13" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W13" s="3" t="s">
+      <c r="W13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="X13" s="4" t="s">
+      <c r="X13" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y13" s="3" t="s">
+      <c r="Y13" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="Z13" s="3" t="s">
+      <c r="Z13" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AA13" s="3" t="s">
+      <c r="AA13" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="O14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="T14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="V14" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="W14" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="X14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="O15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="R15" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T15" s="3" t="s">
+      <c r="T15" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V15" s="3" t="s">
+      <c r="V15" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W15" s="3" t="s">
+      <c r="W15" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X15" s="4" t="s">
+      <c r="X15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y15" s="3" t="s">
+      <c r="Y15" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="Z15" s="3" t="s">
+      <c r="Z15" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AA15" s="3" t="s">
+      <c r="AA15" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="O16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" s="4" t="s">
+      <c r="P16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="S16" s="3" t="s">
+      <c r="S16" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T16" s="3" t="s">
+      <c r="T16" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="U16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V16" s="3" t="s">
+      <c r="V16" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W16" s="3" t="s">
+      <c r="W16" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="X16" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y16" s="3" t="s">
+      <c r="Y16" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="Z16" s="3" t="s">
+      <c r="Z16" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AA16" s="3" t="s">
+      <c r="AA16" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="O17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" s="4" t="s">
+      <c r="P17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="S17" s="3" t="s">
+      <c r="S17" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T17" s="3" t="s">
+      <c r="T17" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V17" s="3" t="s">
+      <c r="V17" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W17" s="3" t="s">
+      <c r="W17" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X17" s="4" t="s">
+      <c r="X17" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y17" s="3" t="s">
+      <c r="Y17" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="Z17" s="3" t="s">
+      <c r="Z17" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AA17" s="3" t="s">
+      <c r="AA17" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="O18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="R18" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="S18" s="3" t="s">
+      <c r="S18" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T18" s="3" t="s">
+      <c r="T18" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V18" s="3" t="s">
+      <c r="V18" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W18" s="3" t="s">
+      <c r="W18" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X18" s="4" t="s">
+      <c r="X18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y18" s="3" t="s">
+      <c r="Y18" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="Z18" s="3" t="s">
+      <c r="Z18" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="AA18" s="3" t="s">
+      <c r="AA18" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="C19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="1" t="n">
         <v>20000</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="O19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="R19" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="S19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="T19" s="3" t="s">
+      <c r="T19" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="V19" s="3" t="s">
+      <c r="V19" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="W19" s="3" t="s">
+      <c r="W19" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X19" s="4" t="s">
+      <c r="X19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="Y19" s="3" t="s">
+      <c r="Y19" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="Z19" s="3" t="s">
+      <c r="Z19" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="AA19" s="3" t="s">
+      <c r="AA19" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="1" t="n">
         <v>26500</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2" t="s">
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P20" s="2"/>
-      <c r="R20" s="4" t="s">
+      <c r="P20" s="1"/>
+      <c r="R20" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="S20" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="T20" s="3" t="s">
+      <c r="T20" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="U20" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="V20" s="3" t="s">
+      <c r="V20" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="W20" s="3" t="s">
+      <c r="W20" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="X20" s="3" t="s">
+      <c r="X20" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="Y20" s="3" t="s">
+      <c r="Y20" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="Z20" s="3" t="s">
+      <c r="Z20" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AA20" s="3" t="s">
+      <c r="AA20" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="C21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I21" s="1" t="n">
         <v>42000</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="O21" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="R21" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="S21" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="T21" s="3" t="s">
+      <c r="T21" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="U21" s="3" t="s">
+      <c r="U21" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="V21" s="3" t="s">
+      <c r="V21" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="W21" s="3" t="s">
+      <c r="W21" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X21" s="4" t="s">
+      <c r="X21" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="Z21" s="3" t="s">
+      <c r="Z21" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AA21" s="3" t="s">
+      <c r="AA21" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="C22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" s="1" t="n">
         <v>42000</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="O22" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="R22" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="S22" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="T22" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="U22" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="V22" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="W22" s="3" t="s">
+      <c r="W22" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X22" s="4" t="s">
+      <c r="X22" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="Z22" s="3" t="s">
+      <c r="Z22" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AA22" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="C23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I23" s="1" t="n">
         <v>56000</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="O23" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="R23" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="S23" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="T23" s="3" t="s">
+      <c r="T23" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="U23" s="3" t="s">
+      <c r="U23" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="V23" s="3" t="s">
+      <c r="V23" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="W23" s="3" t="s">
+      <c r="W23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X23" s="3" t="s">
+      <c r="X23" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="Z23" s="3" t="s">
+      <c r="Z23" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AA23" s="3" t="s">
+      <c r="AA23" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="C24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N24" s="2" t="n">
+      <c r="M24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="O24" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" s="4" t="s">
+      <c r="P24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="S24" s="3" t="s">
+      <c r="S24" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="T24" s="3" t="s">
+      <c r="T24" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="U24" s="3" t="s">
+      <c r="U24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="V24" s="3" t="s">
+      <c r="V24" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="W24" s="3" t="s">
+      <c r="W24" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="X24" s="3" t="s">
+      <c r="X24" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="Z24" s="3" t="s">
+      <c r="Z24" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="AA24" s="3" t="s">
+      <c r="AA24" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="C25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>206</v>
       </c>
       <c r="I25" s="0" t="n">
         <v>54000</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N25" s="2" t="n">
+      <c r="M25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="O25" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="4" t="s">
+      <c r="P25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="S25" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="T25" s="3" t="s">
+      <c r="T25" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="U25" s="3" t="s">
+      <c r="U25" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V25" s="3" t="s">
+      <c r="V25" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="W25" s="3" t="s">
+      <c r="W25" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="X25" s="3" t="s">
+      <c r="X25" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="Z25" s="3" t="s">
+      <c r="Z25" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AA25" s="3" t="s">
+      <c r="AA25" s="1" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="C26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I26" s="1" t="n">
         <v>40000</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="O26" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="R26" s="4" t="s">
+      <c r="R26" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="S26" s="3" t="s">
+      <c r="S26" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="T26" s="3" t="s">
+      <c r="T26" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="U26" s="3" t="s">
+      <c r="U26" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="V26" s="3" t="s">
+      <c r="V26" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="W26" s="3" t="s">
+      <c r="W26" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="X26" s="3" t="s">
+      <c r="X26" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="Z26" s="3" t="s">
+      <c r="Z26" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="AA26" s="3" t="s">
+      <c r="AA26" s="1" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="C27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="I27" s="1" t="n">
         <v>50000</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="O27" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="R27" s="4" t="s">
+      <c r="R27" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="S27" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="T27" s="3" t="s">
+      <c r="T27" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="U27" s="3" t="s">
+      <c r="U27" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="V27" s="3" t="s">
+      <c r="V27" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="W27" s="3" t="s">
+      <c r="W27" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="X27" s="3" t="s">
+      <c r="X27" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="Z27" s="3" t="s">
+      <c r="Z27" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="AA27" s="3" t="s">
+      <c r="AA27" s="1" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="C28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="I28" s="1" t="n">
         <v>7400</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="O28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R28" s="4" t="s">
+      <c r="R28" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="S28" s="3" t="s">
+      <c r="S28" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="T28" s="3" t="s">
+      <c r="T28" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="U28" s="3" t="s">
+      <c r="U28" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="V28" s="3" t="s">
+      <c r="V28" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="W28" s="3" t="s">
+      <c r="W28" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="X28" s="3" t="s">
+      <c r="X28" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="Y28" s="3" t="s">
+      <c r="Y28" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="Z28" s="3" t="s">
+      <c r="Z28" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="AA28" s="3" t="s">
+      <c r="AA28" s="1" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I29" s="2" t="n">
+      <c r="I29" s="1" t="n">
         <v>12000</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="O29" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R29" s="4" t="s">
+      <c r="R29" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="S29" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="T29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="V29" s="3" t="s">
+      <c r="V29" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="W29" s="4" t="s">
+      <c r="W29" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="X29" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Y29" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Z29" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="AA29" s="3" t="s">
+      <c r="AA29" s="1" t="s">
         <v>296</v>
       </c>
     </row>
@@ -3038,114 +3028,114 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3166,175 +3156,175 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A41"/>
-  <sheetFormatPr defaultColWidth="8.484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>358</v>
       </c>
     </row>
@@ -3355,102 +3345,102 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>275</v>
       </c>
     </row>
